--- a/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/Input from Raghukanth/HazardData_sks_v1.xlsx
+++ b/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/Input from Raghukanth/HazardData_sks_v1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sks\OneDrive\PhD_SKS\codes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\OpenSees_PracticeExamples\ida-spo-msa\HazardAnalysis\gm-selection\2020_NBC_MyCopy_new-main\Input from Raghukanth\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="844" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="HazCur-STGR-2026-08-12" sheetId="1" r:id="rId1"/>
@@ -298,9 +298,6 @@
     <t>Δ (proposedCode - PSHA_new)</t>
   </si>
   <si>
-    <t>PSHA_new (STGR-2026-08-12)</t>
-  </si>
-  <si>
     <t>PSHA_old (STGR c. 2020)</t>
   </si>
   <si>
@@ -443,6 +440,9 @@
       </rPr>
       <t>(g)</t>
     </r>
+  </si>
+  <si>
+    <t>PSHA_new (STGR-2026-08-18)</t>
   </si>
 </sst>
 </file>
@@ -988,7 +988,7 @@
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="10" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1063,10 +1063,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -18648,7 +18644,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Guwa-HazCur-STGR-2026-08-18'!$A$22:$A$36</c15:sqref>
@@ -18708,7 +18704,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Guwa-HazCur-STGR-2026-08-18'!$AB$22:$AB$36</c15:sqref>
@@ -18767,7 +18763,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000001-B564-48F1-A1F7-6A2C5792036E}"/>
                   </c:ext>
@@ -18795,7 +18791,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Guwa-HazCur-STGR-2026-08-18'!$A$22:$A$36</c15:sqref>
@@ -18855,7 +18851,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Guwa-HazCur-STGR-2026-08-18'!$G$22:$G$36</c15:sqref>
@@ -18914,7 +18910,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000002-B564-48F1-A1F7-6A2C5792036E}"/>
                   </c:ext>
@@ -18942,7 +18938,7 @@
                 </c:marker>
                 <c:xVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Guwa-HazCur-STGR-2026-08-18'!$A$22:$A$36</c15:sqref>
@@ -19002,7 +18998,7 @@
                 </c:xVal>
                 <c:yVal>
                   <c:numRef>
-                    <c:extLst>
+                    <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                       <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
                           <c15:sqref>'Guwa-HazCur-STGR-2026-08-18'!$P$22:$P$36</c15:sqref>
@@ -19061,7 +19057,7 @@
                   </c:numRef>
                 </c:yVal>
                 <c:smooth val="1"/>
-                <c:extLst>
+                <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
                   <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                     <c16:uniqueId val="{00000003-B564-48F1-A1F7-6A2C5792036E}"/>
                   </c:ext>
@@ -36318,24 +36314,24 @@
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="84" t="s">
+      <c r="A50" s="80" t="s">
         <v>39</v>
       </c>
-      <c r="B50" s="85" t="s">
+      <c r="B50" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="C50" s="87" t="s">
+      <c r="C50" s="83" t="s">
         <v>36</v>
       </c>
-      <c r="D50" s="89" t="s">
+      <c r="D50" s="85" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="90"/>
+      <c r="E50" s="86"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="84"/>
-      <c r="B51" s="86"/>
-      <c r="C51" s="88"/>
+      <c r="A51" s="80"/>
+      <c r="B51" s="82"/>
+      <c r="C51" s="84"/>
       <c r="D51" s="4" t="s">
         <v>37</v>
       </c>
@@ -37416,10 +37412,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K61"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" customWidth="1"/>
     <col min="2" max="2" width="11.28515625" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="5" width="13.28515625" customWidth="1"/>
@@ -37432,7 +37428,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="51" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -37543,8 +37539,8 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="91" t="s">
-        <v>73</v>
+      <c r="A4" s="87" t="s">
+        <v>72</v>
       </c>
       <c r="B4" s="16" t="s">
         <v>56</v>
@@ -37578,7 +37574,7 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="92"/>
+      <c r="A5" s="88"/>
       <c r="B5" s="20" t="s">
         <v>57</v>
       </c>
@@ -37611,7 +37607,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="93"/>
+      <c r="A6" s="89"/>
       <c r="B6" s="23" t="s">
         <v>58</v>
       </c>
@@ -37645,46 +37641,46 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
-        <v>72</v>
+        <v>99</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="40">
+      <c r="C8" s="36">
         <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(C3),OFFSET($D$17,MATCH(LN(C3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(C3),$E$17:$E$56,-1)-1, 0, 2)))</f>
-        <v>9.8514519652933508E-2</v>
-      </c>
-      <c r="D8" s="40">
-        <f t="shared" ref="D8:K8" ca="1" si="1">EXP(_xlfn.FORECAST.LINEAR(LN(D3),OFFSET($D$17,MATCH(LN(D3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(D3),$E$17:$E$56,-1)-1, 0, 2)))</f>
-        <v>0.16403536188218668</v>
-      </c>
-      <c r="E8" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.21161472311263774</v>
-      </c>
-      <c r="F8" s="43">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.28213836440923856</v>
-      </c>
-      <c r="G8" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.39674932901846038</v>
-      </c>
-      <c r="H8" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.4467670683793537</v>
-      </c>
-      <c r="I8" s="43">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.58558136894400481</v>
-      </c>
-      <c r="J8" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.74684504422921372</v>
-      </c>
-      <c r="K8" s="40">
-        <f t="shared" ca="1" si="1"/>
-        <v>0.94116065555108752</v>
+        <v>0.17867739752642309</v>
+      </c>
+      <c r="D8" s="36">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(D3),OFFSET($D$17,MATCH(LN(D3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(D3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>0.28442291031123901</v>
+      </c>
+      <c r="E8" s="36">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(E3),OFFSET($D$17,MATCH(LN(E3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(E3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>0.35460621855982061</v>
+      </c>
+      <c r="F8" s="39">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(F3),OFFSET($D$17,MATCH(LN(F3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(F3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>0.45815856043204828</v>
+      </c>
+      <c r="G8" s="36">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(G3),OFFSET($D$17,MATCH(LN(G3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(G3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>0.60789625946555659</v>
+      </c>
+      <c r="H8" s="36">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(H3),OFFSET($D$17,MATCH(LN(H3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(H3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>0.67552947356117743</v>
+      </c>
+      <c r="I8" s="39">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(I3),OFFSET($D$17,MATCH(LN(I3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(I3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>0.86448020839074347</v>
+      </c>
+      <c r="J8" s="36">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(J3),OFFSET($D$17,MATCH(LN(J3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(J3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>1.0861546848248769</v>
+      </c>
+      <c r="K8" s="36">
+        <f ca="1">EXP(_xlfn.FORECAST.LINEAR(LN(K3),OFFSET($D$17,MATCH(LN(K3),$E$17:$E$56,-1)-1, 0, 2),OFFSET($E$17,MATCH(LN(K3),$E$17:$E$56,-1)-1, 0, 2)))</f>
+        <v>1.3635444334267732</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -37694,99 +37690,99 @@
       <c r="B9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C9" s="40">
+      <c r="C9" s="36">
         <v>0.3</v>
       </c>
-      <c r="D9" s="40">
+      <c r="D9" s="36">
         <v>0.375</v>
       </c>
-      <c r="E9" s="40">
+      <c r="E9" s="36">
         <v>0.45</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="39">
         <v>0.5</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="36">
         <v>0.6</v>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="36">
         <v>0.625</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="39">
         <v>0.75</v>
       </c>
-      <c r="J9" s="40">
+      <c r="J9" s="36">
         <v>0.94</v>
       </c>
-      <c r="K9" s="40">
+      <c r="K9" s="36">
         <v>1.125</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="45" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="46" t="s">
+      <c r="A10" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="42" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="48">
+      <c r="C10" s="43"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="44">
         <v>0.39</v>
       </c>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="48">
+      <c r="G10" s="43"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="44">
         <v>0.77</v>
       </c>
-      <c r="J10" s="40"/>
-      <c r="K10" s="40"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
+      <c r="A11" s="40" t="s">
         <v>70</v>
       </c>
       <c r="B11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E11" s="39"/>
-      <c r="F11" s="42">
+      <c r="E11" s="35"/>
+      <c r="F11" s="38">
         <f ca="1">(F8-F6)/F6</f>
-        <v>0.17950821241320472</v>
-      </c>
-      <c r="I11" s="42">
+        <v>0.91537859712394765</v>
+      </c>
+      <c r="I11" s="38">
         <f ca="1">(I8-I6)/I6</f>
-        <v>0.10507901291565346</v>
+        <v>0.63140254461359391</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="44" t="s">
+      <c r="A12" s="40" t="s">
         <v>71</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="38">
         <f ca="1">(F9-F8)/F8</f>
-        <v>0.77218011824423693</v>
-      </c>
-      <c r="I12" s="42">
+        <v>9.1325237988557517E-2</v>
+      </c>
+      <c r="I12" s="38">
         <f ca="1">(I9-I8)/I8</f>
-        <v>0.28077845330444151</v>
+        <v>-0.13242663889766995</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="44"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="11"/>
-      <c r="F13" s="42"/>
-      <c r="I13" s="42"/>
+      <c r="F13" s="38"/>
+      <c r="I13" s="38"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="94" t="s">
+      <c r="B14" s="90" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="95"/>
+      <c r="C14" s="91"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" s="30" t="s">
@@ -37795,10 +37791,10 @@
       <c r="C15" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="37" t="s">
         <v>68</v>
       </c>
     </row>
@@ -37817,672 +37813,244 @@
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B17" s="34">
-        <v>1E-4</v>
-      </c>
-      <c r="C17" s="35">
-        <v>5.908095883205533</v>
-      </c>
-      <c r="D17" s="38">
+      <c r="B17">
+        <v>1E-3</v>
+      </c>
+      <c r="C17">
+        <v>2.1312701615552503</v>
+      </c>
+      <c r="D17" s="34">
         <f>LN(B17)</f>
-        <v>-9.2103403719761818</v>
-      </c>
-      <c r="E17" s="38">
+        <v>-6.9077552789821368</v>
+      </c>
+      <c r="E17" s="34">
         <f>LN(C17)</f>
-        <v>1.776323593922261</v>
+        <v>0.75671812197221755</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="34">
-        <v>1.264855E-4</v>
-      </c>
-      <c r="C18" s="35">
-        <v>5.6157982642762363</v>
-      </c>
-      <c r="D18" s="38">
-        <f t="shared" ref="D18:D56" si="2">LN(B18)</f>
-        <v>-8.9753828808725196</v>
-      </c>
-      <c r="E18" s="38">
-        <f t="shared" ref="E18:E56" si="3">LN(C18)</f>
-        <v>1.7255837444750795</v>
+      <c r="B18">
+        <v>1.8374400000000001E-3</v>
+      </c>
+      <c r="C18">
+        <v>1.6199987672975</v>
+      </c>
+      <c r="D18" s="34">
+        <f t="shared" ref="D18:D31" si="1">LN(B18)</f>
+        <v>-6.2993819804716296</v>
+      </c>
+      <c r="E18" s="34">
+        <f t="shared" ref="E18:E31" si="2">LN(C18)</f>
+        <v>0.48242538831653409</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="34">
-        <v>1.599859E-4</v>
-      </c>
-      <c r="C19" s="35">
-        <v>5.288259997498244</v>
-      </c>
-      <c r="D19" s="38">
+      <c r="B19">
+        <v>3.37617E-3</v>
+      </c>
+      <c r="C19">
+        <v>1.1306651352853749</v>
+      </c>
+      <c r="D19" s="34">
+        <f t="shared" si="1"/>
+        <v>-5.6910133480659821</v>
+      </c>
+      <c r="E19" s="34">
         <f t="shared" si="2"/>
-        <v>-8.7404248716136834</v>
-      </c>
-      <c r="E19" s="38">
-        <f t="shared" si="3"/>
-        <v>1.6654892687949876</v>
+        <v>0.12280607485500615</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B20" s="34">
-        <v>2.0235899999999999E-4</v>
-      </c>
-      <c r="C20" s="35">
-        <v>4.932238485198468</v>
-      </c>
-      <c r="D20" s="38">
+      <c r="B20">
+        <v>6.2034899999999999E-3</v>
+      </c>
+      <c r="C20">
+        <v>0.72412785882087505</v>
+      </c>
+      <c r="D20" s="34">
+        <f t="shared" si="1"/>
+        <v>-5.0826432420758767</v>
+      </c>
+      <c r="E20" s="34">
         <f t="shared" si="2"/>
-        <v>-8.5054672102408304</v>
-      </c>
-      <c r="E20" s="38">
-        <f t="shared" si="3"/>
-        <v>1.5957929387961607</v>
+        <v>-0.32278730160714852</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="34">
-        <v>2.5595480000000002E-4</v>
-      </c>
-      <c r="C21" s="35">
-        <v>4.5559072559699416</v>
-      </c>
-      <c r="D21" s="38">
+      <c r="B21">
+        <v>1.1398500000000001E-2</v>
+      </c>
+      <c r="C21">
+        <v>0.42673315898874753</v>
+      </c>
+      <c r="D21" s="34">
+        <f t="shared" si="1"/>
+        <v>-4.4742735111863245</v>
+      </c>
+      <c r="E21" s="34">
         <f t="shared" si="2"/>
-        <v>-8.2705096915737055</v>
-      </c>
-      <c r="E21" s="38">
-        <f t="shared" si="3"/>
-        <v>1.5164246889181137</v>
+        <v>-0.8515963814987132</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B22" s="34">
-        <v>3.2374580000000001E-4</v>
-      </c>
-      <c r="C22" s="35">
-        <v>4.1680081523954868</v>
-      </c>
-      <c r="D22" s="38">
+      <c r="B22">
+        <v>2.09441E-2</v>
+      </c>
+      <c r="C22">
+        <v>0.23222993279245127</v>
+      </c>
+      <c r="D22" s="34">
+        <f t="shared" si="1"/>
+        <v>-3.8658982951888641</v>
+      </c>
+      <c r="E22" s="34">
         <f t="shared" si="2"/>
-        <v>-8.0355519180076485</v>
-      </c>
-      <c r="E22" s="38">
-        <f t="shared" si="3"/>
-        <v>1.4274382603981661</v>
+        <v>-1.4600273084982514</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="34">
-        <v>4.0949150000000001E-4</v>
-      </c>
-      <c r="C23" s="35">
-        <v>3.7769307119306181</v>
-      </c>
-      <c r="D23" s="38">
+      <c r="B23">
+        <v>3.8483299999999998E-2</v>
+      </c>
+      <c r="C23">
+        <v>0.11738344911526809</v>
+      </c>
+      <c r="D23" s="34">
+        <f t="shared" si="1"/>
+        <v>-3.2575308980259514</v>
+      </c>
+      <c r="E23" s="34">
         <f t="shared" si="2"/>
-        <v>-7.8005944119073369</v>
-      </c>
-      <c r="E23" s="38">
-        <f t="shared" si="3"/>
-        <v>1.3289116988256533</v>
+        <v>-2.1423093601017835</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="34">
-        <v>5.179475E-4</v>
-      </c>
-      <c r="C24" s="35">
-        <v>3.390166056575254</v>
-      </c>
-      <c r="D24" s="38">
+      <c r="B24">
+        <v>7.0710700000000001E-2</v>
+      </c>
+      <c r="C24">
+        <v>5.4654558448240555E-2</v>
+      </c>
+      <c r="D24" s="34">
+        <f t="shared" si="1"/>
+        <v>-2.6491583738251139</v>
+      </c>
+      <c r="E24" s="34">
         <f t="shared" si="2"/>
-        <v>-7.5656366721925377</v>
-      </c>
-      <c r="E24" s="38">
-        <f t="shared" si="3"/>
-        <v>1.2208789044331581</v>
+        <v>-2.9067226561594572</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="34">
-        <v>6.5512860000000003E-4</v>
-      </c>
-      <c r="C25" s="35">
-        <v>3.0140202215407039</v>
-      </c>
-      <c r="D25" s="38">
+      <c r="B25">
+        <v>0.12992600000000001</v>
+      </c>
+      <c r="C25">
+        <v>2.2812588272380176E-2</v>
+      </c>
+      <c r="D25" s="34">
+        <f t="shared" si="1"/>
+        <v>-2.0407902213691274</v>
+      </c>
+      <c r="E25" s="34">
         <f t="shared" si="2"/>
-        <v>-7.3306790057225255</v>
-      </c>
-      <c r="E25" s="38">
-        <f t="shared" si="3"/>
-        <v>1.1032748093857467</v>
+        <v>-3.7804427781727137</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="34">
-        <v>8.2864280000000004E-4</v>
-      </c>
-      <c r="C26" s="35">
-        <v>2.6535293023334821</v>
-      </c>
-      <c r="D26" s="38">
+      <c r="B26">
+        <v>0.238731</v>
+      </c>
+      <c r="C26">
+        <v>8.1814487195800614E-3</v>
+      </c>
+      <c r="D26" s="34">
+        <f t="shared" si="1"/>
+        <v>-1.4324178839398778</v>
+      </c>
+      <c r="E26" s="34">
         <f t="shared" si="2"/>
-        <v>-7.0957213762637004</v>
-      </c>
-      <c r="E26" s="38">
-        <f t="shared" si="3"/>
-        <v>0.97589056612421166</v>
+        <v>-4.805886038965598</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="34">
-        <v>1.048113E-3</v>
-      </c>
-      <c r="C27" s="35">
-        <v>2.3125683418475091</v>
-      </c>
-      <c r="D27" s="38">
+      <c r="B27">
+        <v>0.43865300000000002</v>
+      </c>
+      <c r="C27">
+        <v>2.3515541229573991E-3</v>
+      </c>
+      <c r="D27" s="34">
+        <f t="shared" si="1"/>
+        <v>-0.82404661126550938</v>
+      </c>
+      <c r="E27" s="34">
         <f t="shared" si="2"/>
-        <v>-6.8607638744684412</v>
-      </c>
-      <c r="E27" s="38">
-        <f t="shared" si="3"/>
-        <v>0.83835874319911041</v>
+        <v>-6.0526788404896319</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B28" s="34">
-        <v>1.325711E-3</v>
-      </c>
-      <c r="C28" s="35">
-        <v>1.993954722885974</v>
-      </c>
-      <c r="D28" s="38">
+      <c r="B28">
+        <v>0.80599699999999996</v>
+      </c>
+      <c r="C28">
+        <v>5.0057823607384375E-4</v>
+      </c>
+      <c r="D28" s="34">
+        <f t="shared" si="1"/>
+        <v>-0.21567525856680303</v>
+      </c>
+      <c r="E28" s="34">
         <f t="shared" si="2"/>
-        <v>-6.6258063596906887</v>
-      </c>
-      <c r="E28" s="38">
-        <f t="shared" si="3"/>
-        <v>0.69011996460480196</v>
+        <v>-7.5997466555931901</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B29" s="34">
-        <v>1.676833E-3</v>
-      </c>
-      <c r="C29" s="35">
-        <v>1.6997255242895331</v>
-      </c>
-      <c r="D29" s="38">
+      <c r="B29">
+        <v>1.4809699999999999</v>
+      </c>
+      <c r="C29">
+        <v>7.7867155937875465E-5</v>
+      </c>
+      <c r="D29" s="34">
+        <f t="shared" si="1"/>
+        <v>0.39269727849710473</v>
+      </c>
+      <c r="E29" s="34">
         <f t="shared" si="2"/>
-        <v>-6.390848383687695</v>
-      </c>
-      <c r="E29" s="38">
-        <f t="shared" si="3"/>
-        <v>0.53046678172642414</v>
+        <v>-9.4605063122493096</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B30" s="34">
-        <v>2.1209509999999998E-3</v>
-      </c>
-      <c r="C30" s="35">
-        <v>1.431243818427901</v>
-      </c>
-      <c r="D30" s="38">
+      <c r="B30">
+        <v>2.7211799999999999</v>
+      </c>
+      <c r="C30">
+        <v>8.2645346739632316E-6</v>
+      </c>
+      <c r="D30" s="34">
+        <f t="shared" si="1"/>
+        <v>1.0010656097630972</v>
+      </c>
+      <c r="E30" s="34">
         <f t="shared" si="2"/>
-        <v>-6.1558907059766854</v>
-      </c>
-      <c r="E30" s="38">
-        <f t="shared" si="3"/>
-        <v>0.35854386930874593</v>
+        <v>-11.703537129067133</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="34">
-        <v>2.682696E-3</v>
-      </c>
-      <c r="C31" s="35">
-        <v>1.189409613900352</v>
-      </c>
-      <c r="D31" s="38">
+      <c r="B31">
+        <v>5</v>
+      </c>
+      <c r="C31">
+        <v>5.6149103500747975E-7</v>
+      </c>
+      <c r="D31" s="34">
+        <f t="shared" si="1"/>
+        <v>1.6094379124341003</v>
+      </c>
+      <c r="E31" s="34">
         <f t="shared" si="2"/>
-        <v>-5.9209330199590049</v>
-      </c>
-      <c r="E31" s="38">
-        <f t="shared" si="3"/>
-        <v>0.17345706124100174</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B32" s="34">
-        <v>3.393222E-3</v>
-      </c>
-      <c r="C32" s="35">
-        <v>0.97464939196652278</v>
-      </c>
-      <c r="D32" s="38">
-        <f t="shared" si="2"/>
-        <v>-5.6859753664963666</v>
-      </c>
-      <c r="E32" s="38">
-        <f t="shared" si="3"/>
-        <v>-2.567747063820228E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B33" s="34">
-        <v>4.2919339999999999E-3</v>
-      </c>
-      <c r="C33" s="35">
-        <v>0.78697227066732012</v>
-      </c>
-      <c r="D33" s="38">
-        <f t="shared" si="2"/>
-        <v>-5.4510178317783309</v>
-      </c>
-      <c r="E33" s="38">
-        <f t="shared" si="3"/>
-        <v>-0.23956226540743025</v>
-      </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B34" s="34">
-        <v>5.428675E-3</v>
-      </c>
-      <c r="C34" s="35">
-        <v>0.62586014264525147</v>
-      </c>
-      <c r="D34" s="38">
-        <f t="shared" si="2"/>
-        <v>-5.2160601895456971</v>
-      </c>
-      <c r="E34" s="38">
-        <f t="shared" si="3"/>
-        <v>-0.46862834714744217</v>
-      </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B35" s="34">
-        <v>6.8664879999999996E-3</v>
-      </c>
-      <c r="C35" s="35">
-        <v>0.49018576629532618</v>
-      </c>
-      <c r="D35" s="38">
-        <f t="shared" si="2"/>
-        <v>-4.9811025116106977</v>
-      </c>
-      <c r="E35" s="38">
-        <f t="shared" si="3"/>
-        <v>-0.71297084483493534</v>
-      </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="34">
-        <v>8.6851140000000007E-3</v>
-      </c>
-      <c r="C36" s="35">
-        <v>0.37823593342545792</v>
-      </c>
-      <c r="D36" s="38">
-        <f t="shared" si="2"/>
-        <v>-4.7461447532957672</v>
-      </c>
-      <c r="E36" s="38">
-        <f t="shared" si="3"/>
-        <v>-0.97223711556973635</v>
-      </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="34">
-        <v>1.0985409999999999E-2</v>
-      </c>
-      <c r="C37" s="35">
-        <v>0.28772647768619208</v>
-      </c>
-      <c r="D37" s="38">
-        <f t="shared" si="2"/>
-        <v>-4.5111872502189501</v>
-      </c>
-      <c r="E37" s="38">
-        <f t="shared" si="3"/>
-        <v>-1.2457449803820002</v>
-      </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="34">
-        <v>1.389495E-2</v>
-      </c>
-      <c r="C38" s="35">
-        <v>0.21600190183744411</v>
-      </c>
-      <c r="D38" s="38">
-        <f t="shared" si="2"/>
-        <v>-4.2762298142108408</v>
-      </c>
-      <c r="E38" s="38">
-        <f t="shared" si="3"/>
-        <v>-1.532468066533752</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="34">
-        <v>1.7575110000000001E-2</v>
-      </c>
-      <c r="C39" s="35">
-        <v>0.1602190604962743</v>
-      </c>
-      <c r="D39" s="38">
-        <f t="shared" si="2"/>
-        <v>-4.0412715824145256</v>
-      </c>
-      <c r="E39" s="38">
-        <f t="shared" si="3"/>
-        <v>-1.8312132720478704</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="34">
-        <v>2.222996E-2</v>
-      </c>
-      <c r="C40" s="35">
-        <v>0.1175477097727792</v>
-      </c>
-      <c r="D40" s="38">
-        <f t="shared" si="2"/>
-        <v>-3.8063143503778711</v>
-      </c>
-      <c r="E40" s="38">
-        <f t="shared" si="3"/>
-        <v>-2.1409109871907104</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="34">
-        <v>2.8117690000000001E-2</v>
-      </c>
-      <c r="C41" s="35">
-        <v>8.5402565253673401E-2</v>
-      </c>
-      <c r="D41" s="38">
-        <f t="shared" si="2"/>
-        <v>-3.5713563633514105</v>
-      </c>
-      <c r="E41" s="38">
-        <f t="shared" si="3"/>
-        <v>-2.4603791405395272</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="34">
-        <v>3.5564800000000001E-2</v>
-      </c>
-      <c r="C42" s="35">
-        <v>6.1491962566833501E-2</v>
-      </c>
-      <c r="D42" s="38">
-        <f t="shared" si="2"/>
-        <v>-3.3363988943187266</v>
-      </c>
-      <c r="E42" s="38">
-        <f t="shared" si="3"/>
-        <v>-2.7888488026805303</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="34">
-        <v>4.4984330000000003E-2</v>
-      </c>
-      <c r="C43" s="35">
-        <v>4.3901457669789999E-2</v>
-      </c>
-      <c r="D43" s="38">
-        <f t="shared" si="2"/>
-        <v>-3.1014410720774763</v>
-      </c>
-      <c r="E43" s="38">
-        <f t="shared" si="3"/>
-        <v>-3.1258077551290282</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="34">
-        <v>5.6898659999999997E-2</v>
-      </c>
-      <c r="C44" s="35">
-        <v>3.1084822974548801E-2</v>
-      </c>
-      <c r="D44" s="38">
-        <f t="shared" si="2"/>
-        <v>-2.866483488215033</v>
-      </c>
-      <c r="E44" s="38">
-        <f t="shared" si="3"/>
-        <v>-3.4710355861604749</v>
-      </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="34">
-        <v>7.1968569999999996E-2</v>
-      </c>
-      <c r="C45" s="35">
-        <v>2.18023868669678E-2</v>
-      </c>
-      <c r="D45" s="38">
-        <f t="shared" si="2"/>
-        <v>-2.6315257830498466</v>
-      </c>
-      <c r="E45" s="38">
-        <f t="shared" si="3"/>
-        <v>-3.8257358258701615</v>
-      </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="34">
-        <v>9.1029819999999997E-2</v>
-      </c>
-      <c r="C46" s="35">
-        <v>1.51336448834697E-2</v>
-      </c>
-      <c r="D46" s="38">
-        <f t="shared" si="2"/>
-        <v>-2.3965681338369924</v>
-      </c>
-      <c r="E46" s="38">
-        <f t="shared" si="3"/>
-        <v>-4.1908348758014382</v>
-      </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="34">
-        <v>0.11513950000000001</v>
-      </c>
-      <c r="C47" s="35">
-        <v>1.03845140074554E-2</v>
-      </c>
-      <c r="D47" s="38">
-        <f t="shared" si="2"/>
-        <v>-2.1616108422834195</v>
-      </c>
-      <c r="E47" s="38">
-        <f t="shared" si="3"/>
-        <v>-4.5674396202979306</v>
-      </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="34">
-        <v>0.14563480000000001</v>
-      </c>
-      <c r="C48" s="35">
-        <v>7.0239158449112004E-3</v>
-      </c>
-      <c r="D48" s="38">
-        <f t="shared" si="2"/>
-        <v>-1.9266531607891164</v>
-      </c>
-      <c r="E48" s="38">
-        <f t="shared" si="3"/>
-        <v>-4.9584344037986581</v>
-      </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="34">
-        <v>0.18420700000000001</v>
-      </c>
-      <c r="C49" s="35">
-        <v>4.6731057329906997E-3</v>
-      </c>
-      <c r="D49" s="38">
-        <f t="shared" si="2"/>
-        <v>-1.6916951537114422</v>
-      </c>
-      <c r="E49" s="38">
-        <f t="shared" si="3"/>
-        <v>-5.3659313891575904</v>
-      </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="34">
-        <v>0.23299520000000001</v>
-      </c>
-      <c r="C50" s="35">
-        <v>3.0554395638375002E-3</v>
-      </c>
-      <c r="D50" s="38">
-        <f t="shared" si="2"/>
-        <v>-1.4567374264870061</v>
-      </c>
-      <c r="E50" s="38">
-        <f t="shared" si="3"/>
-        <v>-5.7908318132922743</v>
-      </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="34">
-        <v>0.2947052</v>
-      </c>
-      <c r="C51" s="35">
-        <v>1.9340661838214001E-3</v>
-      </c>
-      <c r="D51" s="38">
-        <f t="shared" si="2"/>
-        <v>-1.2217797443313847</v>
-      </c>
-      <c r="E51" s="38">
-        <f t="shared" si="3"/>
-        <v>-6.2481306613259155</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="34">
-        <v>0.37275940000000002</v>
-      </c>
-      <c r="C52" s="35">
-        <v>1.1808560293502001E-3</v>
-      </c>
-      <c r="D52" s="38">
-        <f t="shared" si="2"/>
-        <v>-0.98682210768074319</v>
-      </c>
-      <c r="E52" s="38">
-        <f t="shared" si="3"/>
-        <v>-6.7415156549133437</v>
-      </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="34">
-        <v>0.47148659999999998</v>
-      </c>
-      <c r="C53" s="35">
-        <v>6.9445905194239995E-4</v>
-      </c>
-      <c r="D53" s="38">
-        <f t="shared" si="2"/>
-        <v>-0.75186459724885224</v>
-      </c>
-      <c r="E53" s="38">
-        <f t="shared" si="3"/>
-        <v>-7.2723773579942188</v>
-      </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="34">
-        <v>0.59636230000000001</v>
-      </c>
-      <c r="C54" s="35">
-        <v>3.8603226678899998E-4</v>
-      </c>
-      <c r="D54" s="38">
-        <f t="shared" si="2"/>
-        <v>-0.51690691069854211</v>
-      </c>
-      <c r="E54" s="38">
-        <f t="shared" si="3"/>
-        <v>-7.8595895992755036</v>
-      </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="34">
-        <v>0.75431199999999998</v>
-      </c>
-      <c r="C55" s="35">
-        <v>1.952882885234E-4</v>
-      </c>
-      <c r="D55" s="38">
-        <f t="shared" si="2"/>
-        <v>-0.2819492034594891</v>
-      </c>
-      <c r="E55" s="38">
-        <f t="shared" si="3"/>
-        <v>-8.5410336884777642</v>
-      </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="34">
-        <v>0.95409549999999999</v>
-      </c>
-      <c r="C56" s="35">
-        <v>9.6211213531205444E-5</v>
-      </c>
-      <c r="D56" s="38">
-        <f t="shared" si="2"/>
-        <v>-4.6991507722200926E-2</v>
-      </c>
-      <c r="E56" s="38">
-        <f t="shared" si="3"/>
-        <v>-9.2489646423123126</v>
-      </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="34">
-        <v>1.206793</v>
-      </c>
-      <c r="C57" s="35"/>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="34">
-        <v>1.5264180000000001</v>
-      </c>
-      <c r="C58" s="35"/>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="34">
-        <v>1.930698</v>
-      </c>
-      <c r="C59" s="35"/>
-    </row>
-    <row r="60" spans="2:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="36">
-        <v>2.442053</v>
-      </c>
-      <c r="C60" s="37"/>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="2"/>
-      <c r="C61" s="2"/>
+        <v>-14.392670029044119</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -38507,89 +38075,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="54" t="s">
+      <c r="Q1" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" s="54" t="s">
+      <c r="S1" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="54" t="s">
+      <c r="T1" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="54" t="s">
+      <c r="V1" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="V1" s="54" t="s">
+      <c r="W1" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="W1" s="54" t="s">
+      <c r="X1" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="X1" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="54" t="s">
+      <c r="Z1" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="Z1" s="54" t="s">
+      <c r="AA1" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="AA1" s="54" t="s">
+      <c r="AB1" s="50" t="s">
         <v>84</v>
-      </c>
-      <c r="AB1" s="54" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
@@ -39883,103 +39451,103 @@
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="49">
+      <c r="A19" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="45">
         <v>1.85</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="50"/>
+      <c r="A20" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="46"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="54" t="s">
+      <c r="A21" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="54" t="s">
+      <c r="B21" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="54" t="s">
+      <c r="C21" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="54" t="s">
+      <c r="D21" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="54" t="s">
+      <c r="E21" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="54" t="s">
+      <c r="F21" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="54" t="s">
+      <c r="G21" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="54" t="s">
+      <c r="H21" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="54" t="s">
+      <c r="I21" s="50" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="50" t="s">
+        <v>12</v>
+      </c>
+      <c r="L21" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="50" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="50" t="s">
+        <v>16</v>
+      </c>
+      <c r="O21" s="50" t="s">
+        <v>17</v>
+      </c>
+      <c r="P21" s="50" t="s">
         <v>75</v>
       </c>
-      <c r="J21" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="K21" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="M21" s="54" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="O21" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="P21" s="54" t="s">
+      <c r="Q21" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="R21" s="50" t="s">
         <v>76</v>
       </c>
-      <c r="Q21" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="R21" s="54" t="s">
+      <c r="S21" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="S21" s="54" t="s">
+      <c r="T21" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" s="50" t="s">
         <v>78</v>
       </c>
-      <c r="T21" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="U21" s="54" t="s">
+      <c r="V21" s="50" t="s">
         <v>79</v>
       </c>
-      <c r="V21" s="54" t="s">
+      <c r="W21" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="W21" s="54" t="s">
+      <c r="X21" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y21" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="X21" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y21" s="54" t="s">
+      <c r="Z21" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="Z21" s="54" t="s">
+      <c r="AA21" s="50" t="s">
         <v>83</v>
       </c>
-      <c r="AA21" s="54" t="s">
+      <c r="AB21" s="50" t="s">
         <v>84</v>
-      </c>
-      <c r="AB21" s="54" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
@@ -41678,42 +41246,42 @@
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A42" s="50" t="s">
+      <c r="A42" s="46" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A43" s="80" t="s">
+      <c r="A43" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="80" t="s">
+      <c r="B43" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="80" t="s">
+      <c r="C43" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="96" t="s">
+      <c r="D43" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="97"/>
-      <c r="F43" s="97"/>
-      <c r="G43" s="97"/>
+      <c r="E43" s="93"/>
+      <c r="F43" s="93"/>
+      <c r="G43" s="93"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A44" s="80"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="80"/>
-      <c r="D44" s="80" t="s">
+      <c r="A44" s="76"/>
+      <c r="B44" s="76"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="E44" s="80" t="s">
+      <c r="E44" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="80" t="s">
+      <c r="F44" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="76" t="s">
         <v>95</v>
-      </c>
-      <c r="G44" s="80" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
@@ -41771,28 +41339,28 @@
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A47" s="52">
+      <c r="A47" s="48">
         <v>475</v>
       </c>
-      <c r="B47" s="52">
+      <c r="B47" s="48">
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="C47" s="53">
+      <c r="C47" s="49">
         <v>0.5</v>
       </c>
-      <c r="D47" s="53">
+      <c r="D47" s="49">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="E47" s="53">
+      <c r="E47" s="49">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="F47" s="53">
+      <c r="F47" s="49">
         <f t="shared" si="5"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="G47" s="53">
+      <c r="G47" s="49">
         <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
@@ -41852,28 +41420,28 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="52">
+      <c r="A50" s="48">
         <v>2475</v>
       </c>
-      <c r="B50" s="52">
+      <c r="B50" s="48">
         <v>4.0404040404040404E-4</v>
       </c>
-      <c r="C50" s="53">
+      <c r="C50" s="49">
         <v>0.75</v>
       </c>
-      <c r="D50" s="53">
+      <c r="D50" s="49">
         <f t="shared" si="3"/>
         <v>0.75</v>
       </c>
-      <c r="E50" s="53">
+      <c r="E50" s="49">
         <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
-      <c r="F50" s="53">
+      <c r="F50" s="49">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="G50" s="53">
+      <c r="G50" s="49">
         <f t="shared" si="6"/>
         <v>0.375</v>
       </c>
@@ -41934,45 +41502,45 @@
     </row>
     <row r="53" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A54" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="B54" s="71" t="s">
+      <c r="A54" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="B54" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="C54" s="68" t="s">
         <v>92</v>
-      </c>
-      <c r="C54" s="72" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="73">
+      <c r="A55" s="69">
         <v>1E-3</v>
       </c>
-      <c r="B55" s="75">
+      <c r="B55" s="71">
         <f>1/475</f>
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="C55" s="76">
+      <c r="C55" s="72">
         <f>1/2475</f>
         <v>4.0404040404040404E-4</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="74">
+      <c r="A56" s="70">
         <v>4</v>
       </c>
-      <c r="B56" s="77">
+      <c r="B56" s="73">
         <f>B55</f>
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="C56" s="78">
+      <c r="C56" s="74">
         <f>C55</f>
         <v>4.0404040404040404E-4</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C58" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D58" s="3">
         <v>0</v>
@@ -41989,113 +41557,113 @@
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C59" s="3"/>
-      <c r="D59" s="51" t="s">
+      <c r="D59" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="E59" s="51" t="s">
+      <c r="E59" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="F59" s="51" t="s">
+      <c r="F59" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="G59" s="47" t="s">
         <v>95</v>
-      </c>
-      <c r="G59" s="51" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C60" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" s="79">
+        <v>89</v>
+      </c>
+      <c r="D60" s="75">
         <v>1</v>
       </c>
-      <c r="E60" s="79">
+      <c r="E60" s="75">
         <f>(1/E58)</f>
         <v>1</v>
       </c>
-      <c r="F60" s="79">
+      <c r="F60" s="75">
         <f t="shared" ref="F60:G60" si="7">(1/F58)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="G60" s="79">
+      <c r="G60" s="75">
         <f t="shared" si="7"/>
         <v>0.5</v>
       </c>
     </row>
     <row r="82" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A82" s="56" t="s">
+      <c r="A82" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="64" t="s">
+      <c r="A83" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="B83" s="57">
+      <c r="B83" s="53">
         <v>75</v>
       </c>
-      <c r="C83" s="57">
+      <c r="C83" s="53">
         <v>175</v>
       </c>
-      <c r="D83" s="57">
+      <c r="D83" s="53">
         <v>275</v>
       </c>
-      <c r="E83" s="65">
+      <c r="E83" s="61">
         <v>475</v>
       </c>
-      <c r="F83" s="57">
+      <c r="F83" s="53">
         <v>975</v>
       </c>
-      <c r="G83" s="57">
+      <c r="G83" s="53">
         <v>1275</v>
       </c>
-      <c r="H83" s="65">
+      <c r="H83" s="61">
         <v>2475</v>
       </c>
-      <c r="I83" s="57">
+      <c r="I83" s="53">
         <v>4975</v>
       </c>
-      <c r="J83" s="58">
+      <c r="J83" s="54">
         <v>9975</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="66" t="s">
+      <c r="A84" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="B84" s="67">
+      <c r="B84" s="63">
         <f>1/B83</f>
         <v>1.3333333333333334E-2</v>
       </c>
-      <c r="C84" s="67">
+      <c r="C84" s="63">
         <f t="shared" ref="C84:J84" si="8">1/C83</f>
         <v>5.7142857142857143E-3</v>
       </c>
-      <c r="D84" s="67">
+      <c r="D84" s="63">
         <f t="shared" si="8"/>
         <v>3.6363636363636364E-3</v>
       </c>
-      <c r="E84" s="68">
+      <c r="E84" s="64">
         <f t="shared" si="8"/>
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="F84" s="67">
+      <c r="F84" s="63">
         <f t="shared" si="8"/>
         <v>1.0256410256410256E-3</v>
       </c>
-      <c r="G84" s="67">
+      <c r="G84" s="63">
         <f t="shared" si="8"/>
         <v>7.8431372549019605E-4</v>
       </c>
-      <c r="H84" s="68">
+      <c r="H84" s="64">
         <f t="shared" si="8"/>
         <v>4.0404040404040404E-4</v>
       </c>
-      <c r="I84" s="67">
+      <c r="I84" s="63">
         <f t="shared" si="8"/>
         <v>2.0100502512562814E-4</v>
       </c>
-      <c r="J84" s="69">
+      <c r="J84" s="65">
         <f t="shared" si="8"/>
         <v>1.0025062656641604E-4</v>
       </c>
@@ -42104,31 +41672,31 @@
       <c r="A85" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B85" s="57">
+      <c r="B85" s="53">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="C85" s="57">
+      <c r="C85" s="53">
         <v>3.4599999999999999E-2</v>
       </c>
-      <c r="D85" s="57">
+      <c r="D85" s="53">
         <v>4.36E-2</v>
       </c>
-      <c r="E85" s="57">
+      <c r="E85" s="53">
         <v>5.6899999999999999E-2</v>
       </c>
-      <c r="F85" s="57">
+      <c r="F85" s="53">
         <v>7.8299999999999995E-2</v>
       </c>
-      <c r="G85" s="57">
+      <c r="G85" s="53">
         <v>8.6900000000000005E-2</v>
       </c>
-      <c r="H85" s="57">
+      <c r="H85" s="53">
         <v>0.11119999999999999</v>
       </c>
-      <c r="I85" s="57">
+      <c r="I85" s="53">
         <v>0.14269999999999999</v>
       </c>
-      <c r="J85" s="58">
+      <c r="J85" s="54">
         <v>0.1822</v>
       </c>
     </row>
@@ -42136,73 +41704,73 @@
       <c r="A86" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B86" s="59">
+      <c r="B86" s="55">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="C86" s="59">
+      <c r="C86" s="55">
         <v>7.2300000000000003E-2</v>
       </c>
-      <c r="D86" s="59">
+      <c r="D86" s="55">
         <v>9.6799999999999997E-2</v>
       </c>
-      <c r="E86" s="59">
+      <c r="E86" s="55">
         <v>0.1353</v>
       </c>
-      <c r="F86" s="59">
+      <c r="F86" s="55">
         <v>0.2049</v>
       </c>
-      <c r="G86" s="59">
+      <c r="G86" s="55">
         <v>0.23699999999999999</v>
       </c>
-      <c r="H86" s="59">
+      <c r="H86" s="55">
         <v>0.33300000000000002</v>
       </c>
-      <c r="I86" s="59">
+      <c r="I86" s="55">
         <v>0.46029999999999999</v>
       </c>
-      <c r="J86" s="60">
+      <c r="J86" s="56">
         <v>0.61229999999999996</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="61" t="s">
+      <c r="A87" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B87" s="62">
+      <c r="B87" s="58">
         <v>7.6499999999999999E-2</v>
       </c>
-      <c r="C87" s="62">
+      <c r="C87" s="58">
         <v>0.13089999999999999</v>
       </c>
-      <c r="D87" s="62">
+      <c r="D87" s="58">
         <v>0.1736</v>
       </c>
-      <c r="E87" s="62">
+      <c r="E87" s="58">
         <v>0.2392</v>
       </c>
-      <c r="F87" s="62">
+      <c r="F87" s="58">
         <v>0.34949999999999998</v>
       </c>
-      <c r="G87" s="62">
+      <c r="G87" s="58">
         <v>0.39689999999999998</v>
       </c>
-      <c r="H87" s="62">
+      <c r="H87" s="58">
         <v>0.52990000000000004</v>
       </c>
-      <c r="I87" s="62">
+      <c r="I87" s="58">
         <v>0.69689999999999996</v>
       </c>
-      <c r="J87" s="63">
+      <c r="J87" s="59">
         <v>0.89090000000000003</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A90" s="56" t="s">
-        <v>98</v>
+      <c r="A90" s="52" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="61" t="s">
+      <c r="A91" s="57" t="s">
         <v>58</v>
       </c>
       <c r="B91">
@@ -42234,12 +41802,12 @@
       </c>
     </row>
     <row r="93" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A93" s="56" t="s">
-        <v>97</v>
+      <c r="A93" s="52" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="61" t="s">
+      <c r="A94" s="57" t="s">
         <v>58</v>
       </c>
       <c r="B94">
@@ -42271,12 +41839,12 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A96" s="56" t="s">
-        <v>99</v>
+      <c r="A96" s="52" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="61" t="s">
+      <c r="A97" s="57" t="s">
         <v>58</v>
       </c>
       <c r="B97">
@@ -42331,89 +41899,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="49" t="s">
+      <c r="F1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="49" t="s">
+      <c r="G1" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="M1" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="N1" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="P1" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="L1" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="P1" s="49" t="s">
+      <c r="Q1" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="Q1" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" s="49" t="s">
+      <c r="S1" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="S1" s="49" t="s">
+      <c r="T1" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="T1" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="49" t="s">
+      <c r="V1" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="V1" s="49" t="s">
+      <c r="W1" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="W1" s="49" t="s">
+      <c r="X1" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y1" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="X1" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="49" t="s">
+      <c r="Z1" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="Z1" s="49" t="s">
+      <c r="AA1" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="AA1" s="49" t="s">
+      <c r="AB1" s="45" t="s">
         <v>84</v>
-      </c>
-      <c r="AB1" s="49" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
@@ -43707,103 +43275,103 @@
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A19" s="49" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="49">
+      <c r="A19" s="45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="45">
         <v>1.85</v>
       </c>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A20" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="B20" s="50"/>
+      <c r="A20" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B20" s="46"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A21" s="49" t="s">
+      <c r="A21" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="49" t="s">
+      <c r="B21" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C21" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D21" s="49" t="s">
+      <c r="D21" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="E21" s="49" t="s">
+      <c r="E21" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="49" t="s">
+      <c r="F21" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G21" s="49" t="s">
+      <c r="G21" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="H21" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="49" t="s">
+      <c r="I21" s="45" t="s">
+        <v>74</v>
+      </c>
+      <c r="J21" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="K21" s="45" t="s">
+        <v>12</v>
+      </c>
+      <c r="L21" s="45" t="s">
+        <v>13</v>
+      </c>
+      <c r="M21" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="N21" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="O21" s="45" t="s">
+        <v>17</v>
+      </c>
+      <c r="P21" s="45" t="s">
         <v>75</v>
       </c>
-      <c r="J21" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="K21" s="49" t="s">
-        <v>12</v>
-      </c>
-      <c r="L21" s="49" t="s">
-        <v>13</v>
-      </c>
-      <c r="M21" s="49" t="s">
-        <v>14</v>
-      </c>
-      <c r="N21" s="49" t="s">
-        <v>16</v>
-      </c>
-      <c r="O21" s="49" t="s">
-        <v>17</v>
-      </c>
-      <c r="P21" s="49" t="s">
+      <c r="Q21" s="45" t="s">
+        <v>18</v>
+      </c>
+      <c r="R21" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="Q21" s="49" t="s">
-        <v>18</v>
-      </c>
-      <c r="R21" s="49" t="s">
+      <c r="S21" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="S21" s="49" t="s">
+      <c r="T21" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="U21" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="T21" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="U21" s="49" t="s">
+      <c r="V21" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="V21" s="49" t="s">
+      <c r="W21" s="45" t="s">
         <v>80</v>
       </c>
-      <c r="W21" s="49" t="s">
+      <c r="X21" s="45" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y21" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="X21" s="49" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y21" s="49" t="s">
+      <c r="Z21" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="Z21" s="49" t="s">
+      <c r="AA21" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="AA21" s="49" t="s">
+      <c r="AB21" s="45" t="s">
         <v>84</v>
-      </c>
-      <c r="AB21" s="49" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:28" x14ac:dyDescent="0.25">
@@ -45502,42 +45070,42 @@
       </c>
     </row>
     <row r="42" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A42" s="50" t="s">
+      <c r="A42" s="46" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A43" s="80" t="s">
+      <c r="A43" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="80" t="s">
+      <c r="B43" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="80" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="98" t="s">
+      <c r="C43" s="76" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="95"/>
     </row>
     <row r="44" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A44" s="51"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="80" t="s">
+      <c r="A44" s="47"/>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="E44" s="80" t="s">
+      <c r="E44" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="80" t="s">
+      <c r="F44" s="76" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="76" t="s">
         <v>95</v>
-      </c>
-      <c r="G44" s="80" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:28" x14ac:dyDescent="0.25">
@@ -45595,28 +45163,28 @@
       </c>
     </row>
     <row r="47" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A47" s="52">
+      <c r="A47" s="48">
         <v>475</v>
       </c>
-      <c r="B47" s="52">
+      <c r="B47" s="48">
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="C47" s="53">
+      <c r="C47" s="49">
         <v>0.33300000000000002</v>
       </c>
-      <c r="D47" s="53">
+      <c r="D47" s="49">
         <f t="shared" si="3"/>
         <v>0.33300000000000002</v>
       </c>
-      <c r="E47" s="53">
+      <c r="E47" s="49">
         <f t="shared" si="4"/>
         <v>0.33300000000000002</v>
       </c>
-      <c r="F47" s="53">
+      <c r="F47" s="49">
         <f t="shared" si="5"/>
         <v>0.222</v>
       </c>
-      <c r="G47" s="53">
+      <c r="G47" s="49">
         <f t="shared" si="6"/>
         <v>0.16650000000000001</v>
       </c>
@@ -45676,28 +45244,28 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="52">
+      <c r="A50" s="48">
         <v>2475</v>
       </c>
-      <c r="B50" s="52">
+      <c r="B50" s="48">
         <v>4.0404040404040404E-4</v>
       </c>
-      <c r="C50" s="53">
+      <c r="C50" s="49">
         <v>0.5</v>
       </c>
-      <c r="D50" s="53">
+      <c r="D50" s="49">
         <f t="shared" si="3"/>
         <v>0.5</v>
       </c>
-      <c r="E50" s="53">
+      <c r="E50" s="49">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="F50" s="53">
+      <c r="F50" s="49">
         <f t="shared" si="5"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="G50" s="53">
+      <c r="G50" s="49">
         <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
@@ -45776,50 +45344,50 @@
     </row>
     <row r="55" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="B56" s="71" t="s">
+      <c r="A56" s="66" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="C56" s="68" t="s">
         <v>92</v>
-      </c>
-      <c r="C56" s="72" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="73">
+      <c r="A57" s="69">
         <v>1E-3</v>
       </c>
-      <c r="B57" s="75">
+      <c r="B57" s="71">
         <f>1/475</f>
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="C57" s="76">
+      <c r="C57" s="72">
         <f>1/2475</f>
         <v>4.0404040404040404E-4</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="74">
+      <c r="A58" s="70">
         <v>4</v>
       </c>
-      <c r="B58" s="77">
+      <c r="B58" s="73">
         <f>B57</f>
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="C58" s="78">
+      <c r="C58" s="74">
         <f>C57</f>
         <v>4.0404040404040404E-4</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A59" s="83"/>
-      <c r="B59" s="75"/>
-      <c r="C59" s="75"/>
+      <c r="A59" s="79"/>
+      <c r="B59" s="71"/>
+      <c r="C59" s="71"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C60" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D60" s="3">
         <v>0</v>
@@ -45836,22 +45404,22 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C61" s="3"/>
-      <c r="D61" s="51" t="s">
+      <c r="D61" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="E61" s="51" t="s">
+      <c r="E61" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="F61" s="51" t="s">
+      <c r="F61" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="G61" s="47" t="s">
         <v>95</v>
-      </c>
-      <c r="G61" s="51" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C62" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -45859,89 +45427,89 @@
       <c r="E62" s="3">
         <v>1</v>
       </c>
-      <c r="F62" s="79">
+      <c r="F62" s="75">
         <f>(1/F60)</f>
         <v>0.66666666666666663</v>
       </c>
-      <c r="G62" s="79">
+      <c r="G62" s="75">
         <f>(1/G60)</f>
         <v>0.5</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="56" t="s">
+      <c r="A67" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="64" t="s">
+      <c r="A68" s="60" t="s">
         <v>59</v>
       </c>
-      <c r="B68" s="57">
+      <c r="B68" s="53">
         <v>75</v>
       </c>
-      <c r="C68" s="57">
+      <c r="C68" s="53">
         <v>175</v>
       </c>
-      <c r="D68" s="57">
+      <c r="D68" s="53">
         <v>275</v>
       </c>
-      <c r="E68" s="65">
+      <c r="E68" s="61">
         <v>475</v>
       </c>
-      <c r="F68" s="57">
+      <c r="F68" s="53">
         <v>975</v>
       </c>
-      <c r="G68" s="57">
+      <c r="G68" s="53">
         <v>1275</v>
       </c>
-      <c r="H68" s="65">
+      <c r="H68" s="61">
         <v>2475</v>
       </c>
-      <c r="I68" s="57">
+      <c r="I68" s="53">
         <v>4975</v>
       </c>
-      <c r="J68" s="58">
+      <c r="J68" s="54">
         <v>9975</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="66" t="s">
+      <c r="A69" s="62" t="s">
         <v>60</v>
       </c>
-      <c r="B69" s="67">
+      <c r="B69" s="63">
         <f>1/B68</f>
         <v>1.3333333333333334E-2</v>
       </c>
-      <c r="C69" s="67">
+      <c r="C69" s="63">
         <f t="shared" ref="C69:J69" si="7">1/C68</f>
         <v>5.7142857142857143E-3</v>
       </c>
-      <c r="D69" s="67">
+      <c r="D69" s="63">
         <f t="shared" si="7"/>
         <v>3.6363636363636364E-3</v>
       </c>
-      <c r="E69" s="68">
+      <c r="E69" s="64">
         <f t="shared" si="7"/>
         <v>2.1052631578947368E-3</v>
       </c>
-      <c r="F69" s="67">
+      <c r="F69" s="63">
         <f t="shared" si="7"/>
         <v>1.0256410256410256E-3</v>
       </c>
-      <c r="G69" s="67">
+      <c r="G69" s="63">
         <f t="shared" si="7"/>
         <v>7.8431372549019605E-4</v>
       </c>
-      <c r="H69" s="68">
+      <c r="H69" s="64">
         <f t="shared" si="7"/>
         <v>4.0404040404040404E-4</v>
       </c>
-      <c r="I69" s="67">
+      <c r="I69" s="63">
         <f t="shared" si="7"/>
         <v>2.0100502512562814E-4</v>
       </c>
-      <c r="J69" s="69">
+      <c r="J69" s="65">
         <f t="shared" si="7"/>
         <v>1.0025062656641604E-4</v>
       </c>
@@ -45950,31 +45518,31 @@
       <c r="A70" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B70" s="57">
+      <c r="B70" s="53">
         <v>2.1899999999999999E-2</v>
       </c>
-      <c r="C70" s="57">
+      <c r="C70" s="53">
         <v>3.4599999999999999E-2</v>
       </c>
-      <c r="D70" s="57">
+      <c r="D70" s="53">
         <v>4.36E-2</v>
       </c>
-      <c r="E70" s="57">
+      <c r="E70" s="53">
         <v>5.6899999999999999E-2</v>
       </c>
-      <c r="F70" s="57">
+      <c r="F70" s="53">
         <v>7.8299999999999995E-2</v>
       </c>
-      <c r="G70" s="57">
+      <c r="G70" s="53">
         <v>8.6900000000000005E-2</v>
       </c>
-      <c r="H70" s="57">
+      <c r="H70" s="53">
         <v>0.11119999999999999</v>
       </c>
-      <c r="I70" s="57">
+      <c r="I70" s="53">
         <v>0.14269999999999999</v>
       </c>
-      <c r="J70" s="58">
+      <c r="J70" s="54">
         <v>0.1822</v>
       </c>
     </row>
@@ -45982,185 +45550,185 @@
       <c r="A71" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B71" s="59">
+      <c r="B71" s="55">
         <v>4.0500000000000001E-2</v>
       </c>
-      <c r="C71" s="59">
+      <c r="C71" s="55">
         <v>7.2300000000000003E-2</v>
       </c>
-      <c r="D71" s="59">
+      <c r="D71" s="55">
         <v>9.6799999999999997E-2</v>
       </c>
-      <c r="E71" s="59">
+      <c r="E71" s="55">
         <v>0.1353</v>
       </c>
-      <c r="F71" s="59">
+      <c r="F71" s="55">
         <v>0.2049</v>
       </c>
-      <c r="G71" s="59">
+      <c r="G71" s="55">
         <v>0.23699999999999999</v>
       </c>
-      <c r="H71" s="59">
+      <c r="H71" s="55">
         <v>0.33300000000000002</v>
       </c>
-      <c r="I71" s="59">
+      <c r="I71" s="55">
         <v>0.46029999999999999</v>
       </c>
-      <c r="J71" s="60">
+      <c r="J71" s="56">
         <v>0.61229999999999996</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="61" t="s">
+      <c r="A72" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="B72" s="62">
+      <c r="B72" s="58">
         <v>7.6499999999999999E-2</v>
       </c>
-      <c r="C72" s="62">
+      <c r="C72" s="58">
         <v>0.13089999999999999</v>
       </c>
-      <c r="D72" s="62">
+      <c r="D72" s="58">
         <v>0.1736</v>
       </c>
-      <c r="E72" s="62">
+      <c r="E72" s="58">
         <v>0.2392</v>
       </c>
-      <c r="F72" s="62">
+      <c r="F72" s="58">
         <v>0.34949999999999998</v>
       </c>
-      <c r="G72" s="62">
+      <c r="G72" s="58">
         <v>0.39689999999999998</v>
       </c>
-      <c r="H72" s="62">
+      <c r="H72" s="58">
         <v>0.52990000000000004</v>
       </c>
-      <c r="I72" s="62">
+      <c r="I72" s="58">
         <v>0.69689999999999996</v>
       </c>
-      <c r="J72" s="63">
+      <c r="J72" s="59">
         <v>0.89090000000000003</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B74" s="82"/>
-      <c r="C74" s="82"/>
-      <c r="D74" s="82"/>
-      <c r="E74" s="82"/>
-      <c r="F74" s="82"/>
-      <c r="G74" s="82"/>
-      <c r="H74" s="82"/>
-      <c r="I74" s="82"/>
-      <c r="J74" s="82"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="78"/>
+      <c r="D74" s="78"/>
+      <c r="E74" s="78"/>
+      <c r="F74" s="78"/>
+      <c r="G74" s="78"/>
+      <c r="H74" s="78"/>
+      <c r="I74" s="78"/>
+      <c r="J74" s="78"/>
     </row>
     <row r="75" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A75" s="56" t="s">
-        <v>98</v>
+      <c r="A75" s="52" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B76" s="81">
+      <c r="B76" s="77">
         <v>3.0534253552491002E-2</v>
       </c>
-      <c r="C76" s="81">
+      <c r="C76" s="77">
         <v>5.2247799204166001E-2</v>
       </c>
-      <c r="D76" s="81">
+      <c r="D76" s="77">
         <v>6.8864213966061003E-2</v>
       </c>
-      <c r="E76" s="81">
+      <c r="E76" s="77">
         <v>9.4689758228719001E-2</v>
       </c>
-      <c r="F76" s="81">
+      <c r="F76" s="77">
         <v>0.14097016526665701</v>
       </c>
-      <c r="G76" s="81">
+      <c r="G76" s="77">
         <v>0.162832985239144</v>
       </c>
-      <c r="H76" s="81">
+      <c r="H76" s="77">
         <v>0.23135077772705301</v>
       </c>
-      <c r="I76" s="81">
+      <c r="I76" s="77">
         <v>0.332024386493319</v>
       </c>
-      <c r="J76" s="81">
+      <c r="J76" s="77">
         <v>0.47259360336538903</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A78" s="56" t="s">
-        <v>97</v>
+      <c r="A78" s="52" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B79" s="81">
+      <c r="B79" s="77">
         <v>2.6119697499103998E-2</v>
       </c>
-      <c r="C79" s="81">
+      <c r="C79" s="77">
         <v>4.4263655745839001E-2</v>
       </c>
-      <c r="D79" s="81">
+      <c r="D79" s="77">
         <v>5.7840751599430001E-2</v>
       </c>
-      <c r="E79" s="81">
+      <c r="E79" s="77">
         <v>7.9059267015249998E-2</v>
       </c>
-      <c r="F79" s="81">
+      <c r="F79" s="77">
         <v>0.116949276929855</v>
       </c>
-      <c r="G79" s="81">
+      <c r="G79" s="77">
         <v>0.13521223795982901</v>
       </c>
-      <c r="H79" s="81">
+      <c r="H79" s="77">
         <v>0.194528978104341</v>
       </c>
-      <c r="I79" s="81">
+      <c r="I79" s="77">
         <v>0.28896669111729101</v>
       </c>
-      <c r="J79" s="81">
+      <c r="J79" s="77">
         <v>0.43849156574250803</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="21" x14ac:dyDescent="0.35">
-      <c r="A81" s="56" t="s">
-        <v>99</v>
+      <c r="A81" s="52" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="B82" s="81">
+      <c r="B82" s="77">
         <v>2.6119697499103998E-2</v>
       </c>
-      <c r="C82" s="81">
+      <c r="C82" s="77">
         <v>4.4263655745839001E-2</v>
       </c>
-      <c r="D82" s="81">
+      <c r="D82" s="77">
         <v>5.7840751599430001E-2</v>
       </c>
-      <c r="E82" s="81">
+      <c r="E82" s="77">
         <v>7.9059267015249998E-2</v>
       </c>
-      <c r="F82" s="81">
+      <c r="F82" s="77">
         <v>0.116949276929855</v>
       </c>
-      <c r="G82" s="81">
+      <c r="G82" s="77">
         <v>0.13521223795982901</v>
       </c>
-      <c r="H82" s="81">
+      <c r="H82" s="77">
         <v>0.194528978104341</v>
       </c>
-      <c r="I82" s="81">
+      <c r="I82" s="77">
         <v>0.28896669111729101</v>
       </c>
-      <c r="J82" s="81">
+      <c r="J82" s="77">
         <v>0.43849156574250803</v>
       </c>
     </row>
